--- a/output/reporte_h2_RM_2025.xlsx
+++ b/output/reporte_h2_RM_2025.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Establecimiento" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Region'!$A$1:$D$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'SS'!$A$1:$E$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Comuna'!$A$1:$F$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Establecimiento'!$A$1:$G$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Region'!$A$1:$D$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'SS'!$A$1:$E$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Comuna'!$A$1:$F$109</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Establecimiento'!$A$1:$G$113</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -490,21 +490,261 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>2275</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>4164</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>0.5463496637848223</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Arica Parinacota</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1759</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1886</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>0.9326617179215271</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>1711</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>1883</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>0.908656399362719</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Aysén del General Carlos Ibañez del Campo</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>547</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>700</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>0.7814285714285715</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>6126</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>6981</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>0.8775247099269445</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>4463</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>5190</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>0.8599229287090558</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>La Araucanía</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>2996</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>3873</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>0.7735605473792926</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Libertador Gral. B. O'Higgins</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>3980</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>4664</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>0.8533447684391081</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>4548</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>4873</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>0.9333059716806895</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>880</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>1181</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>0.7451312447078747</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Magallanes y de la Antártica Chilena</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>847</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>908</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>0.9328193832599119</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
           <t>Maule</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B13" s="3" t="n">
         <v>6762</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="C13" s="3" t="n">
         <v>7572</v>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D13" s="4" t="n">
         <v>0.893026941362916</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>26062</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>29472</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>0.8842969598262758</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>2055</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>3213</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>0.6395891690009337</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>3537</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>4402</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>0.803498409813721</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>2079</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>2487</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>0.8359469240048251</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D2"/>
+  <autoFilter ref="A1:D17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -515,7 +755,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -555,26 +795,635 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Antofagasta</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>2275</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>4164</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>0.5463496637848223</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Arica Parinacota</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1759</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>1886</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>0.9326617179215271</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Atacama</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>1711</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>1883</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>0.908656399362719</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Aysén del General Carlos Ibañez del Campo</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Aysén</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>547</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>0.7814285714285715</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Arauco</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>712</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>947</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>0.7518479408658922</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Biobío</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>1938</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>2136</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>0.9073033707865169</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Concepción</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>2124</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>2453</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>0.8658785161027314</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Talcahuano</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>1352</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>1445</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>0.9356401384083045</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Coquimbo</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>4463</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>5190</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>0.8599229287090558</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>La Araucanía</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Araucanía Norte</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>215</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>249</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>0.8634538152610441</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>La Araucanía</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Araucanía Sur</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>2781</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>3624</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>0.7673841059602649</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Libertador Gral. B. O'Higgins</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>3980</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>4664</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>0.8533447684391081</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Chiloé</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>633</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>679</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>0.9322533136966127</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Reloncaví</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>2659</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>2749</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>0.9672608221171335</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Osorno</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>1256</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>1445</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>0.8692041522491349</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Los Rios</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>880</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>1181</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>0.7451312447078747</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Magallanes y de la Antártica Chilena</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Magallanes</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>847</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>908</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>0.9328193832599119</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
           <t>Maule</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Servicio de Salud Del Maule</t>
         </is>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="C19" s="3" t="n">
         <v>6762</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D19" s="3" t="n">
         <v>7572</v>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="E19" s="4" t="n">
         <v>0.893026941362916</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Central</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>4961</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>5333</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>0.930245640352522</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Norte</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>3775</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>4482</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>0.8422579205711735</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Occidente</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>6159</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>7065</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>0.8717622080679406</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Oriente</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>2559</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>2814</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>0.9093816631130064</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Sur</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>2813</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>2938</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>0.9574540503744043</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Sur Oriente</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>5795</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>6840</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>0.8472222222222222</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Tarapacá</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>2055</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>3213</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>0.6395891690009337</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Aconcagua</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>1676</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>1900</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>0.8821052631578947</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Oriente</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>86</v>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>0.8837209302325582</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Valparaíso San Antonio</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>1784</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>2415</v>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>0.7387163561076605</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Viña del Mar Quillota</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Ñuble</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>2079</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>2487</v>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>0.8359469240048251</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E2"/>
+  <autoFilter ref="A1:E31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -585,7 +1434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -631,102 +1480,102 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Maule</t>
+          <t>Servicio de Salud Antofagasta</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Cauquenes</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>160</v>
+        <v>1156</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>188</v>
+        <v>2450</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>0.851063829787234</v>
+        <v>0.4718367346938775</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Maule</t>
+          <t>Servicio de Salud Antofagasta</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Constitución</t>
+          <t>Calama</t>
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>47</v>
+        <v>1073</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>59</v>
+        <v>1652</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>0.7966101694915254</v>
+        <v>0.6495157384987893</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Maule</t>
+          <t>Servicio de Salud Antofagasta</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Curicó</t>
+          <t>Mejillones</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1946</v>
+        <v>1</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>2062</v>
+        <v>11</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>0.9437439379243453</v>
+        <v>0.09090909090909091</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Maule</t>
+          <t>Servicio de Salud Antofagasta</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Licantén</t>
+          <t>San Pedro de Atacama</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F5" s="4" t="n">
         <v>0</v>
@@ -735,109 +1584,2709 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Maule</t>
+          <t>Servicio de Salud Antofagasta</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Linares</t>
+          <t>Taltal</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1153</v>
+        <v>9</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1437</v>
+        <v>10</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.802366040361865</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Maule</t>
+          <t>Servicio de Salud Antofagasta</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Parral</t>
+          <t>Tocopilla</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>108</v>
+        <v>40</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.6574074074074074</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Arica Parinacota</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Maule</t>
+          <t>Servicio de Salud Arica y Parinacota</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>San Javier</t>
+          <t>Arica</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>78</v>
+        <v>1759</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>100</v>
+        <v>1886</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.78</v>
+        <v>0.9326617179215271</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Atacama</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Chañaral</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Atacama</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Copiapó</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>1140</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>1268</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>0.8990536277602523</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Atacama</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Diego de Almagro</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Atacama</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Vallenar</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>569</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>606</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>0.9389438943894389</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Aysén del General Carlos Ibañez del Campo</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Aysén</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Aisén</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Aysén del General Carlos Ibañez del Campo</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Aysén</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Chile Chico</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Aysén del General Carlos Ibañez del Campo</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Aysén</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Coyhaique</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>538</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>685</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>0.7854014598540145</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Arauco</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Arauco</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Arauco</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Cañete</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>0.6785714285714286</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Arauco</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Curanilahue</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>688</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>909</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>0.7568756875687569</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Arauco</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Lebu</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>0.5555555555555556</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Biobío</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Laja</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Biobío</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Los Ángeles</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>1912</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>2101</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>0.9100428367444074</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Biobío</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Mulchén</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Biobío</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Nacimiento</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Biobío</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Santa Bárbara</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Biobío</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Tucapel</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Biobío</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Yumbel</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Concepción</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Concepción</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>1640</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>1880</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>0.8723404255319149</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Concepción</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Coronel</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>411</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>495</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>0.8303030303030303</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Concepción</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Lota</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>0.9473684210526315</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Concepción</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Santa Juana</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Talcahuano</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Penco</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Talcahuano</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Talcahuano</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>1334</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>1426</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>0.9354838709677419</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Talcahuano</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Tome</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Coquimbo</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>1545</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>1921</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>0.8042686100989068</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Coquimbo</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>369</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>429</v>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>0.8601398601398601</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Coquimbo</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>1389</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>1491</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>0.93158953722334</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Coquimbo</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>0.9555555555555556</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Coquimbo</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>1080</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>1267</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>0.8524072612470402</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Coquimbo</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Coquimbo</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>La Araucanía</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Araucanía Norte</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Angol</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>215</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>248</v>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>0.8669354838709677</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>La Araucanía</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Araucanía Norte</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Collipulli</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>La Araucanía</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Araucanía Sur</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Temuco</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>2781</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>3624</v>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>0.7673841059602649</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Libertador Gral. B. O'Higgins</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Graneros</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Libertador Gral. B. O'Higgins</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Litueche</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Libertador Gral. B. O'Higgins</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Lolol</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F46" s="4" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Libertador Gral. B. O'Higgins</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Nancagua</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F47" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Libertador Gral. B. O'Higgins</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Peumo</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F48" s="4" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Libertador Gral. B. O'Higgins</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Pichidegua</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F49" s="4" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Libertador Gral. B. O'Higgins</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Pichilemu</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Libertador Gral. B. O'Higgins</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Rancagua</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>1737</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>2125</v>
+      </c>
+      <c r="F51" s="4" t="n">
+        <v>0.8174117647058824</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Libertador Gral. B. O'Higgins</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Rengo</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>792</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>957</v>
+      </c>
+      <c r="F52" s="4" t="n">
+        <v>0.8275862068965517</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Libertador Gral. B. O'Higgins</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>San Fernando</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>736</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>791</v>
+      </c>
+      <c r="F53" s="4" t="n">
+        <v>0.9304677623261695</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Libertador Gral. B. O'Higgins</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>San Vicente</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="F54" s="4" t="n">
+        <v>0.8809523809523809</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Libertador Gral. B. O'Higgins</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Santa Cruz</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>666</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>725</v>
+      </c>
+      <c r="F55" s="4" t="n">
+        <v>0.9186206896551724</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Chiloé</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Castro</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>633</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>679</v>
+      </c>
+      <c r="F56" s="4" t="n">
+        <v>0.9322533136966127</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Reloncaví</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Calbuco</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F57" s="4" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Reloncaví</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Frutillar</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F58" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Reloncaví</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Futaleufú</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F59" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Reloncaví</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Puerto Montt</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>2654</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>2739</v>
+      </c>
+      <c r="F60" s="4" t="n">
+        <v>0.9689667761956918</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Osorno</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Osorno</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>1255</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>1443</v>
+      </c>
+      <c r="F61" s="4" t="n">
+        <v>0.8697158697158697</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Osorno</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Purranque</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F62" s="4" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Los Rios</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="F63" s="4" t="n">
+        <v>0.9142857142857143</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Los Rios</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="F64" s="4" t="n">
+        <v>0.8421052631578947</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Los Rios</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="F65" s="4" t="n">
+        <v>0.7903225806451613</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Los Rios</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Río Bueno</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F66" s="4" t="n">
+        <v>0.7058823529411765</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Los Rios</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>723</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>994</v>
+      </c>
+      <c r="F67" s="4" t="n">
+        <v>0.727364185110664</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Magallanes y de la Antártica Chilena</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Magallanes</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>161</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>174</v>
+      </c>
+      <c r="F68" s="4" t="n">
+        <v>0.9252873563218391</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Magallanes y de la Antártica Chilena</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Magallanes</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F69" s="4" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Magallanes y de la Antártica Chilena</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Magallanes</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>685</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>732</v>
+      </c>
+      <c r="F70" s="4" t="n">
+        <v>0.9357923497267759</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
           <t>Maule</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>Servicio de Salud Del Maule</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Cauquenes</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>188</v>
+      </c>
+      <c r="F71" s="4" t="n">
+        <v>0.851063829787234</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Maule</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Constitución</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="F72" s="4" t="n">
+        <v>0.7966101694915254</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Maule</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Curicó</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>1946</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>2062</v>
+      </c>
+      <c r="F73" s="4" t="n">
+        <v>0.9437439379243453</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Maule</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Licantén</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F74" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Maule</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Linares</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>1153</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>1437</v>
+      </c>
+      <c r="F75" s="4" t="n">
+        <v>0.802366040361865</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Maule</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Parral</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>108</v>
+      </c>
+      <c r="F76" s="4" t="n">
+        <v>0.6574074074074074</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Maule</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>San Javier</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F77" s="4" t="n">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Maule</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
         <is>
           <t>Talca</t>
         </is>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D78" s="3" t="n">
         <v>3307</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E78" s="3" t="n">
         <v>3615</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="F78" s="4" t="n">
         <v>0.9147994467496542</v>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Central</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Maipú</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>2197</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>2305</v>
+      </c>
+      <c r="F79" s="4" t="n">
+        <v>0.9531453362255965</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Central</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>2764</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>3028</v>
+      </c>
+      <c r="F80" s="4" t="n">
+        <v>0.9128137384412153</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Norte</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Colina</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F81" s="4" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Norte</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Independencia</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>3774</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>4480</v>
+      </c>
+      <c r="F82" s="4" t="n">
+        <v>0.8424107142857142</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Occidente</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Cerro Navia</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>2296</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>2621</v>
+      </c>
+      <c r="F83" s="4" t="n">
+        <v>0.876001526135063</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Occidente</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Curacaví</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F84" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Occidente</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Melipilla</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>1281</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>1484</v>
+      </c>
+      <c r="F85" s="4" t="n">
+        <v>0.8632075471698113</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Occidente</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Peñaflor</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="F86" s="4" t="n">
+        <v>0.8387096774193549</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Occidente</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="n">
+        <v>1983</v>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>2072</v>
+      </c>
+      <c r="F87" s="4" t="n">
+        <v>0.957046332046332</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Occidente</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Talagante</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>547</v>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>825</v>
+      </c>
+      <c r="F88" s="4" t="n">
+        <v>0.6630303030303031</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Oriente</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Peñalolén</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>2559</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>2814</v>
+      </c>
+      <c r="F89" s="4" t="n">
+        <v>0.9093816631130064</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Sur</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>San Bernardo</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="n">
+        <v>2813</v>
+      </c>
+      <c r="E90" s="3" t="n">
+        <v>2938</v>
+      </c>
+      <c r="F90" s="4" t="n">
+        <v>0.9574540503744043</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Sur Oriente</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>La Florida</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>1899</v>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>2045</v>
+      </c>
+      <c r="F91" s="4" t="n">
+        <v>0.9286063569682151</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Sur Oriente</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Puente Alto</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="n">
+        <v>2261</v>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>2941</v>
+      </c>
+      <c r="F92" s="4" t="n">
+        <v>0.7687861271676301</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Sur Oriente</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>San Ramón</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="n">
+        <v>1635</v>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>1854</v>
+      </c>
+      <c r="F93" s="4" t="n">
+        <v>0.8818770226537217</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Tarapacá</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="E94" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="F94" s="4" t="n">
+        <v>0.9047619047619048</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Tarapacá</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>2036</v>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>3192</v>
+      </c>
+      <c r="F95" s="4" t="n">
+        <v>0.6378446115288221</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Aconcagua</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Llaillay</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Aconcagua</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Los Andes</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>627</v>
+      </c>
+      <c r="E97" s="3" t="n">
+        <v>637</v>
+      </c>
+      <c r="F97" s="4" t="n">
+        <v>0.9843014128728415</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Aconcagua</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>San Felipe</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="n">
+        <v>1049</v>
+      </c>
+      <c r="E98" s="3" t="n">
+        <v>1262</v>
+      </c>
+      <c r="F98" s="4" t="n">
+        <v>0.8312202852614897</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Oriente</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Isla de Pascua</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="E99" s="3" t="n">
+        <v>86</v>
+      </c>
+      <c r="F99" s="4" t="n">
+        <v>0.8837209302325582</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Valparaíso San Antonio</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>San Antonio</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="n">
+        <v>538</v>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v>1038</v>
+      </c>
+      <c r="F100" s="4" t="n">
+        <v>0.5183044315992292</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Valparaíso San Antonio</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="n">
+        <v>1246</v>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v>1377</v>
+      </c>
+      <c r="F101" s="4" t="n">
+        <v>0.9048656499636892</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Viña del Mar Quillota</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Quintero</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E102" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F102" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Ñuble</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E103" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F103" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Ñuble</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="n">
+        <v>1544</v>
+      </c>
+      <c r="E104" s="3" t="n">
+        <v>1934</v>
+      </c>
+      <c r="F104" s="4" t="n">
+        <v>0.7983453981385729</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Ñuble</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E105" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F105" s="4" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Ñuble</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F106" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Ñuble</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E107" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F107" s="4" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Ñuble</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="n">
+        <v>526</v>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>538</v>
+      </c>
+      <c r="F108" s="4" t="n">
+        <v>0.9776951672862454</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Ñuble</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F109" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F9"/>
+  <autoFilter ref="A1:F109"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -848,7 +4297,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -900,122 +4349,122 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Maule</t>
+          <t>Servicio de Salud Antofagasta</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Cauquenes</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Hospital San Juan de Dios (Cauquenes)</t>
+          <t>Hospital Dr. Leonardo Guzmán (Antofagasta)</t>
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v>160</v>
+        <v>1156</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>188</v>
+        <v>2450</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.851063829787234</v>
+        <v>0.4718367346938775</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Maule</t>
+          <t>Servicio de Salud Antofagasta</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Constitución</t>
+          <t>Calama</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Constitución</t>
+          <t>Hospital Dr. Carlos Cisternas (Calama)</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>47</v>
+        <v>1073</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>59</v>
+        <v>1652</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0.7966101694915254</v>
+        <v>0.6495157384987893</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Maule</t>
+          <t>Servicio de Salud Antofagasta</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Curicó</t>
+          <t>Mejillones</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Hospital San Juan de Dios (Curicó)</t>
+          <t>Hospital de Mejillones</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1946</v>
+        <v>1</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>2062</v>
+        <v>11</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.9437439379243453</v>
+        <v>0.09090909090909091</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Maule</t>
+          <t>Servicio de Salud Antofagasta</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Licantén</t>
+          <t>San Pedro de Atacama</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Licantén</t>
+          <t>Centro de Salud Familiar San Pedro Atacama</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>0</v>
@@ -1024,129 +4473,3351 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Maule</t>
+          <t>Servicio de Salud Antofagasta</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Linares</t>
+          <t>Taltal</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Hospital Presidente Carlos Ibáñez del Campo (Linares)</t>
+          <t>Hospital 21 de Mayo (Taltal)</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1153</v>
+        <v>9</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1437</v>
+        <v>10</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.802366040361865</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Maule</t>
+          <t>Servicio de Salud Antofagasta</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Parral</t>
+          <t>Tocopilla</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Hospital San José (Parral)</t>
+          <t>Hospital Dr. Marcos Macuada (Tocopilla)</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>108</v>
+        <v>40</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.6574074074074074</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Arica Parinacota</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Maule</t>
+          <t>Servicio de Salud Arica y Parinacota</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>San Javier</t>
+          <t>Arica</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Hospital Dr. Abel Fuentealba Lagos de San Javier</t>
+          <t>Hospital Regional Dr. Juan Noé Crevani (Arica)</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>78</v>
+        <v>1759</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>100</v>
+        <v>1886</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.78</v>
+        <v>0.9326617179215271</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Atacama</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Chañaral</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Dr. Jerónimo Méndez Arancibia (Chañaral)</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Atacama</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Copiapó</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Hospital San José del Carmen (Copiapó)</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>1140</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>1268</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>0.8990536277602523</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Atacama</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Diego de Almagro</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Dr. Florencio Vargas (Diego de Almagro)</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Atacama</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Vallenar</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Provincial del Huasco Monseñor Fernando Ariztía Ruiz (Vallenar)</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>569</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>606</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>0.9389438943894389</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Aysén del General Carlos Ibañez del Campo</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Aysén</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Aisén</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Hospital de Puerto Aysén</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Aysén del General Carlos Ibañez del Campo</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Aysén</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Chile Chico</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Dr. Leopoldo Ortega Rodríguez (Chile Chico)</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Aysén del General Carlos Ibañez del Campo</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Aysén</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Coyhaique</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Regional de Coyhaique</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>538</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>685</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>0.7854014598540145</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Arauco</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Arauco</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Hospital San Vicente de Arauco</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Arauco</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Cañete</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Intercultural Kallvu Llanka (Cañete)</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>0.6785714285714286</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Arauco</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Curanilahue</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Provincial Dr. Rafael Avaría (Curanilahue)</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>688</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>909</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>0.7568756875687569</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Arauco</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Lebu</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Hospital de Lebu</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>0.5555555555555556</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Biobío</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Laja</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Comunitario de Laja</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Biobío</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Los Ángeles</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Complejo Asistencial Dr. Víctor Ríos Ruiz (Los Ángeles)</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>1912</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>2101</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>0.9100428367444074</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Biobío</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Mulchén</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Hospital de Mulchén</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Biobío</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Nacimiento</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Comunitario y Familiar de Nacimiento</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Biobío</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Santa Bárbara</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Comunitario de Santa Bárbara</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Biobío</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Tucapel</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Comunitario Dr. Roberto Muñoz Urrutia de Huépil</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Biobío</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Yumbel</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Comunitario de Yumbel</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Concepción</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Concepción</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Clínico Regional Dr. Guillermo Grant Benavente (Concepción)</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>1640</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>1880</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>0.8723404255319149</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Concepción</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Coronel</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Hospital San José (Coronel)</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>411</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>495</v>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>0.8303030303030303</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Concepción</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Lota</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Hospital de Lota</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>0.9473684210526315</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Concepción</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Santa Juana</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Clorinda Avello (Santa Juana)</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Talcahuano</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Penco</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Penco Lirquén</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Talcahuano</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Talcahuano</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Las Higueras (Talcahuano)</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>1334</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>1426</v>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>0.9354838709677419</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Talcahuano</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Tome</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Hospital de Tomé</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Coquimbo</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Hospital San Pablo (Coquimbo)</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>1545</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>1921</v>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>0.8042686100989068</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Coquimbo</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Dr. Humberto Elorza Cortés (Illapel)</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>369</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>429</v>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>0.8601398601398601</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Coquimbo</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Hospital San Juan de Dios (La Serena)</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>1389</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>1491</v>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>0.93158953722334</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Coquimbo</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Hospital San Pedro (Los Vilos)</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>0.9555555555555556</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Coquimbo</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Dr. Antonio Tirado Lanas de Ovalle</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>1080</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>1267</v>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v>0.8524072612470402</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Coquimbo</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Hospital de Salamanca</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Coquimbo</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Hospital San Juan de Dios (Vicuña)</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>La Araucanía</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Araucanía Norte</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Angol</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Dr. Mauricio Heyermann (Angol)</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>215</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>248</v>
+      </c>
+      <c r="G41" s="4" t="n">
+        <v>0.8669354838709677</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>La Araucanía</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Araucanía Norte</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Collipulli</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Hospital de Collipulli</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>La Araucanía</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Araucanía Sur</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Temuco</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Dr. Hernán Henríquez Aravena (Temuco)</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>2781</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>3624</v>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>0.7673841059602649</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Libertador Gral. B. O'Higgins</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Graneros</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Santa Filomena de Graneros</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G44" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Libertador Gral. B. O'Higgins</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Litueche</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Hospital de Litueche</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Libertador Gral. B. O'Higgins</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Lolol</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Hospital de Lolol</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G46" s="4" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Libertador Gral. B. O'Higgins</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Nancagua</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Hospital de Nancagua</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G47" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Libertador Gral. B. O'Higgins</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Peumo</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Del Salvador de Peumo</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="G48" s="4" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Libertador Gral. B. O'Higgins</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Pichidegua</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Hospital de Pichidegua</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G49" s="4" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Libertador Gral. B. O'Higgins</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Pichilemu</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Hospital de Pichilemu</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G50" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Libertador Gral. B. O'Higgins</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Rancagua</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Dr. Franco Ravera Zunino</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>1737</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>2125</v>
+      </c>
+      <c r="G51" s="4" t="n">
+        <v>0.8174117647058824</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Libertador Gral. B. O'Higgins</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Rengo</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Dr. Ricardo Valenzuela Sáez (Rengo)</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>792</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>957</v>
+      </c>
+      <c r="G52" s="4" t="n">
+        <v>0.8275862068965517</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Libertador Gral. B. O'Higgins</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>San Fernando</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Centro Comunitario de Salud Familiar Angostura</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Libertador Gral. B. O'Higgins</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>San Fernando</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Hospital San Juan de Dios de San Fernando</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>735</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>790</v>
+      </c>
+      <c r="G54" s="4" t="n">
+        <v>0.930379746835443</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Libertador Gral. B. O'Higgins</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>San Vicente</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Hospital San Vicente de Tagua -Tagua</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="G55" s="4" t="n">
+        <v>0.8809523809523809</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Libertador Gral. B. O'Higgins</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Santa Cruz</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Hospital de Santa Cruz</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>666</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>725</v>
+      </c>
+      <c r="G56" s="4" t="n">
+        <v>0.9186206896551724</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Chiloé</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Castro</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Hospital de Castro</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>633</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>679</v>
+      </c>
+      <c r="G57" s="4" t="n">
+        <v>0.9322533136966127</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Reloncaví</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Calbuco</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Hospital de Calbuco</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G58" s="4" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Reloncaví</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Frutillar</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Hospital de Frutillar</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Reloncaví</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Futaleufú</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Hospital de Futaleufú</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G60" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Reloncaví</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Puerto Montt</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Hospital de Puerto Montt</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>2654</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>2739</v>
+      </c>
+      <c r="G61" s="4" t="n">
+        <v>0.9689667761956918</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Osorno</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Osorno</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Base San José de Osorno</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>1255</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>1443</v>
+      </c>
+      <c r="G62" s="4" t="n">
+        <v>0.8697158697158697</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Osorno</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Purranque</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Hospital de Purranque Dr. Juan Hepp Dubiau</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G63" s="4" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Los Rios</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Juan Morey (La Unión)</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="G64" s="4" t="n">
+        <v>0.9142857142857143</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Los Rios</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Hospital de Paillaco</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="G65" s="4" t="n">
+        <v>0.8421052631578947</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Los Rios</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Hospital de Panguipulli</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="G66" s="4" t="n">
+        <v>0.7903225806451613</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Los Rios</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Río Bueno</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Hospital de Río Bueno</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="G67" s="4" t="n">
+        <v>0.7058823529411765</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Los Rios</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Base Valdivia</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>723</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>994</v>
+      </c>
+      <c r="G68" s="4" t="n">
+        <v>0.727364185110664</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Magallanes y de la Antártica Chilena</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Magallanes</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Dr. Augusto Essmann Burgos ( Natales)</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>161</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>174</v>
+      </c>
+      <c r="G69" s="4" t="n">
+        <v>0.9252873563218391</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Magallanes y de la Antártica Chilena</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Magallanes</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Dr. Marco Antonio Chamorro ( Porvenir)</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G70" s="4" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Magallanes y de la Antártica Chilena</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Magallanes</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Clínico de Magallanes Dr. Lautaro Navarro Avaria</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>685</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>732</v>
+      </c>
+      <c r="G71" s="4" t="n">
+        <v>0.9357923497267759</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
           <t>Maule</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>Servicio de Salud Del Maule</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Cauquenes</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Hospital San Juan de Dios (Cauquenes)</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>188</v>
+      </c>
+      <c r="G72" s="4" t="n">
+        <v>0.851063829787234</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Maule</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Constitución</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Hospital de Constitución</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="G73" s="4" t="n">
+        <v>0.7966101694915254</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Maule</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Curicó</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Hospital San Juan de Dios (Curicó)</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>1946</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>2062</v>
+      </c>
+      <c r="G74" s="4" t="n">
+        <v>0.9437439379243453</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Maule</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Licantén</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Hospital de Licantén</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G75" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Maule</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Linares</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Presidente Carlos Ibáñez del Campo (Linares)</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>1153</v>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>1437</v>
+      </c>
+      <c r="G76" s="4" t="n">
+        <v>0.802366040361865</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Maule</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Parral</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Hospital San José (Parral)</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>108</v>
+      </c>
+      <c r="G77" s="4" t="n">
+        <v>0.6574074074074074</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Maule</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>San Javier</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Dr. Abel Fuentealba Lagos de San Javier</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="G78" s="4" t="n">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Maule</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
         <is>
           <t>Talca</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Hospital Dr. César Garavagno Burotto (Talca)</t>
         </is>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E79" s="3" t="n">
         <v>3307</v>
       </c>
-      <c r="F9" s="3" t="n">
+      <c r="F79" s="3" t="n">
         <v>3615</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="G79" s="4" t="n">
         <v>0.9147994467496542</v>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Central</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Maipú</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Clínico Metropolitano El Carmen Doctor Luis Valentín Ferrada</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>2197</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>2305</v>
+      </c>
+      <c r="G80" s="4" t="n">
+        <v>0.9531453362255965</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Central</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Clínico San Borja Arriarán</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>2764</v>
+      </c>
+      <c r="F81" s="3" t="n">
+        <v>3028</v>
+      </c>
+      <c r="G81" s="4" t="n">
+        <v>0.9128137384412153</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Norte</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Colina</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>SAPU Esmeralda</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F82" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Norte</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Colina</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>SAR Colina</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Norte</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Independencia</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Complejo Hospitalario San José (Santiago, Independencia)</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>3774</v>
+      </c>
+      <c r="F84" s="3" t="n">
+        <v>4480</v>
+      </c>
+      <c r="G84" s="4" t="n">
+        <v>0.8424107142857142</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Occidente</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Cerro Navia</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Hospital  Félix Bulnes Cerda</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>2296</v>
+      </c>
+      <c r="F85" s="3" t="n">
+        <v>2621</v>
+      </c>
+      <c r="G85" s="4" t="n">
+        <v>0.876001526135063</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Occidente</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Curacaví</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Hospital de Curacaví</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Occidente</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Melipilla</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Hospital San José (Melipilla)</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>1281</v>
+      </c>
+      <c r="F87" s="3" t="n">
+        <v>1484</v>
+      </c>
+      <c r="G87" s="4" t="n">
+        <v>0.8632075471698113</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Occidente</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Peñaflor</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Hospital de Peñaflor</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="F88" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="G88" s="4" t="n">
+        <v>0.8387096774193549</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Occidente</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Hospital San Juan de Dios (Santiago, Santiago)</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>1983</v>
+      </c>
+      <c r="F89" s="3" t="n">
+        <v>2072</v>
+      </c>
+      <c r="G89" s="4" t="n">
+        <v>0.957046332046332</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Occidente</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Talagante</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Adalberto Steeger (Talagante)</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="n">
+        <v>547</v>
+      </c>
+      <c r="F90" s="3" t="n">
+        <v>825</v>
+      </c>
+      <c r="G90" s="4" t="n">
+        <v>0.6630303030303031</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Oriente</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Peñalolén</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Dr. Luis Tisné B. (Santiago, Peñalolén)</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>2559</v>
+      </c>
+      <c r="F91" s="3" t="n">
+        <v>2814</v>
+      </c>
+      <c r="G91" s="4" t="n">
+        <v>0.9093816631130064</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Sur</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>San Bernardo</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Hospital El Pino (Santiago, San Bernardo)</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>1544</v>
+      </c>
+      <c r="F92" s="3" t="n">
+        <v>1629</v>
+      </c>
+      <c r="G92" s="4" t="n">
+        <v>0.9478207489257213</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Sur</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>San Bernardo</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Parroquial de San Bernardo (D)</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>1269</v>
+      </c>
+      <c r="F93" s="3" t="n">
+        <v>1309</v>
+      </c>
+      <c r="G93" s="4" t="n">
+        <v>0.9694423223834988</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Sur Oriente</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>La Florida</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Clínico Metropolitano La Florida Dra. Eloísa Díaz Insunza</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="n">
+        <v>1899</v>
+      </c>
+      <c r="F94" s="3" t="n">
+        <v>2045</v>
+      </c>
+      <c r="G94" s="4" t="n">
+        <v>0.9286063569682151</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Sur Oriente</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Puente Alto</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Complejo Hospitalario Dr. Sótero del Río (Santiago, Puente Alto)</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>2261</v>
+      </c>
+      <c r="F95" s="3" t="n">
+        <v>2941</v>
+      </c>
+      <c r="G95" s="4" t="n">
+        <v>0.7687861271676301</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Sur Oriente</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>San Ramón</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Padre Alberto Hurtado (San Ramón)</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>1635</v>
+      </c>
+      <c r="F96" s="3" t="n">
+        <v>1854</v>
+      </c>
+      <c r="G96" s="4" t="n">
+        <v>0.8818770226537217</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Tarapacá</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Centro de Salud Familiar Pedro Pulgar Melgarejo</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" s="4" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Tarapacá</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Hospital de Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F98" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="G98" s="4" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Tarapacá</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Dr. Ernesto Torres Galdames (Iquique)</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="n">
+        <v>2036</v>
+      </c>
+      <c r="F99" s="3" t="n">
+        <v>3192</v>
+      </c>
+      <c r="G99" s="4" t="n">
+        <v>0.6378446115288221</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Aconcagua</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Llaillay</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Hospital San Francisco (Llaillay)</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G100" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Aconcagua</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Los Andes</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Hospital San Juan de Dios (Los Andes)</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v>627</v>
+      </c>
+      <c r="F101" s="3" t="n">
+        <v>637</v>
+      </c>
+      <c r="G101" s="4" t="n">
+        <v>0.9843014128728415</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Aconcagua</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>San Felipe</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Hospital San Camilo de San Felipe</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F102" s="3" t="n">
+        <v>1262</v>
+      </c>
+      <c r="G102" s="4" t="n">
+        <v>0.8312202852614897</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Oriente</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Isla de Pascua</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Hanga Roa (Isla De Pascua)</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="F103" s="3" t="n">
+        <v>86</v>
+      </c>
+      <c r="G103" s="4" t="n">
+        <v>0.8837209302325582</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Valparaíso San Antonio</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>San Antonio</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Claudio Vicuña (San Antonio)</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="n">
+        <v>538</v>
+      </c>
+      <c r="F104" s="3" t="n">
+        <v>1038</v>
+      </c>
+      <c r="G104" s="4" t="n">
+        <v>0.5183044315992292</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Valparaíso San Antonio</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Carlos Van Buren (Valparaíso)</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="n">
+        <v>1246</v>
+      </c>
+      <c r="F105" s="3" t="n">
+        <v>1377</v>
+      </c>
+      <c r="G105" s="4" t="n">
+        <v>0.9048656499636892</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Viña del Mar Quillota</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Quintero</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Adriana Cousiño (Quintero)</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F106" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G106" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Ñuble</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Comunitario de Salud Familiar de Bulnes</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F107" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G107" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Ñuble</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Clínico Herminda Martín (Chillán)</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>1544</v>
+      </c>
+      <c r="F108" s="3" t="n">
+        <v>1934</v>
+      </c>
+      <c r="G108" s="4" t="n">
+        <v>0.7983453981385729</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Ñuble</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Comunitario de Salud Familiar Dr. Eduardo Contreras Trabucco de Coelemu</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F109" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G109" s="4" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Ñuble</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Comunitario de Salud Familiar de El Carmen</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G110" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Ñuble</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Comunitario de Salud Familiar de Quirihue</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F111" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G111" s="4" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Ñuble</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Hospital de San Carlos</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="n">
+        <v>526</v>
+      </c>
+      <c r="F112" s="3" t="n">
+        <v>538</v>
+      </c>
+      <c r="G112" s="4" t="n">
+        <v>0.9776951672862454</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Ñuble</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Comunitario de Salud Familiar Pedro Morales Campos (Yungay)</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G113" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G9"/>
+  <autoFilter ref="A1:G113"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>